--- a/excel/20260316 kafanshan Daily Equipment Breakdown Report.xlsx
+++ b/excel/20260316 kafanshan Daily Equipment Breakdown Report.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E3481B-4226-4CF3-9CD7-6180DD7D6003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B90047F-B3D1-4894-AE09-4D19B4B8DFB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="machines status " sheetId="2" r:id="rId1"/>
@@ -1632,9 +1632,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1672,9 +1672,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1707,9 +1707,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1742,9 +1759,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1919,22 +1953,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A50B941-6D69-4003-B1C6-561792B6526B}">
   <dimension ref="A1:K49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.85546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.88671875" style="6" customWidth="1"/>
     <col min="6" max="6" width="49" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="6"/>
-    <col min="8" max="8" width="10.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="6"/>
+    <col min="7" max="7" width="9.109375" style="6"/>
+    <col min="8" max="8" width="10.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>41</v>
       </c>
@@ -1955,7 +1989,7 @@
       <c r="J1" s="28"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
@@ -1988,7 +2022,7 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -2013,7 +2047,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>2</v>
       </c>
@@ -2032,7 +2066,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>3</v>
       </c>
@@ -2051,7 +2085,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>4</v>
       </c>
@@ -2070,7 +2104,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -2093,7 +2127,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>6</v>
       </c>
@@ -2112,7 +2146,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>7</v>
       </c>
@@ -2131,7 +2165,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>8</v>
       </c>
@@ -2150,7 +2184,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>9</v>
       </c>
@@ -2169,7 +2203,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>10</v>
       </c>
@@ -2194,7 +2228,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>11</v>
       </c>
@@ -2217,7 +2251,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>12</v>
       </c>
@@ -2242,7 +2276,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>13</v>
       </c>
@@ -2261,7 +2295,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>14</v>
       </c>
@@ -2286,7 +2320,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>15</v>
       </c>
@@ -2305,7 +2339,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>16</v>
       </c>
@@ -2324,7 +2358,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -2343,7 +2377,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>18</v>
       </c>
@@ -2362,7 +2396,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>19</v>
       </c>
@@ -2387,7 +2421,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>20</v>
       </c>
@@ -2406,7 +2440,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>21</v>
       </c>
@@ -2425,7 +2459,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>22</v>
       </c>
@@ -2444,7 +2478,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>23</v>
       </c>
@@ -2469,7 +2503,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>24</v>
       </c>
@@ -2488,7 +2522,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>25</v>
       </c>
@@ -2513,7 +2547,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>26</v>
       </c>
@@ -2538,7 +2572,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>27</v>
       </c>
@@ -2557,7 +2591,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>28</v>
       </c>
@@ -2576,7 +2610,7 @@
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>29</v>
       </c>
@@ -2595,7 +2629,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>30</v>
       </c>
@@ -2614,7 +2648,7 @@
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>31</v>
       </c>
@@ -2637,7 +2671,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>32</v>
       </c>
@@ -2662,7 +2696,7 @@
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>33</v>
       </c>
@@ -2681,7 +2715,7 @@
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>34</v>
       </c>
@@ -2706,7 +2740,7 @@
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>35</v>
       </c>
@@ -2731,7 +2765,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>36</v>
       </c>
@@ -2756,7 +2790,7 @@
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>37</v>
       </c>
@@ -2775,7 +2809,7 @@
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>38</v>
       </c>
@@ -2794,7 +2828,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>39</v>
       </c>
@@ -2819,7 +2853,7 @@
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>40</v>
       </c>
@@ -2829,7 +2863,7 @@
       </c>
       <c r="D42" s="10"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>41</v>
       </c>
@@ -2841,7 +2875,7 @@
       </c>
       <c r="D43" s="13"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>42</v>
       </c>
@@ -2853,7 +2887,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>43</v>
       </c>
@@ -2865,7 +2899,7 @@
       </c>
       <c r="D45" s="10"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>44</v>
       </c>
@@ -2882,7 +2916,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>45</v>
       </c>
@@ -2899,7 +2933,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>46</v>
       </c>
@@ -2916,7 +2950,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>47</v>
       </c>
@@ -2942,19 +2976,20 @@
     <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup scale="95" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F240A14-0F8F-4C87-9A01-75B309B2EBE2}">
   <dimension ref="A1:O145"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>72</v>
       </c>
@@ -2980,7 +3015,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
@@ -3006,7 +3041,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -3032,7 +3067,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -3058,7 +3093,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -3078,7 +3113,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -3098,7 +3133,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -3118,7 +3153,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -3144,7 +3179,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -3170,7 +3205,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -3196,7 +3231,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -3222,7 +3257,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -3248,7 +3283,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>104</v>
       </c>
@@ -3274,7 +3309,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>105</v>
       </c>
@@ -3297,7 +3332,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>107</v>
       </c>
@@ -3323,7 +3358,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>109</v>
       </c>
@@ -3349,7 +3384,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>110</v>
       </c>
@@ -3372,7 +3407,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>111</v>
       </c>
@@ -3395,7 +3430,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -3418,7 +3453,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -3441,7 +3476,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -3464,7 +3499,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -3490,7 +3525,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -3516,7 +3551,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>124</v>
       </c>
@@ -3545,7 +3580,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -3574,7 +3609,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -3600,7 +3635,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>131</v>
       </c>
@@ -3629,7 +3664,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>136</v>
       </c>
@@ -3658,7 +3693,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>139</v>
       </c>
@@ -3687,7 +3722,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>141</v>
       </c>
@@ -3716,7 +3751,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>142</v>
       </c>
@@ -3745,7 +3780,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -3768,7 +3803,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>148</v>
       </c>
@@ -3791,7 +3826,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -3814,7 +3849,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -3837,7 +3872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>151</v>
       </c>
@@ -3860,7 +3895,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>152</v>
       </c>
@@ -3883,7 +3918,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>153</v>
       </c>
@@ -3906,7 +3941,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>154</v>
       </c>
@@ -3929,7 +3964,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>155</v>
       </c>
@@ -3952,7 +3987,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -3975,7 +4010,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>159</v>
       </c>
@@ -3998,7 +4033,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>160</v>
       </c>
@@ -4021,7 +4056,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>161</v>
       </c>
@@ -4044,7 +4079,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>162</v>
       </c>
@@ -4067,7 +4102,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>164</v>
       </c>
@@ -4090,7 +4125,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>165</v>
       </c>
@@ -4113,7 +4148,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>166</v>
       </c>
@@ -4136,7 +4171,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>167</v>
       </c>
@@ -4159,7 +4194,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>168</v>
       </c>
@@ -4182,7 +4217,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>169</v>
       </c>
@@ -4205,7 +4240,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>170</v>
       </c>
@@ -4228,7 +4263,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>171</v>
       </c>
@@ -4251,7 +4286,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>173</v>
       </c>
@@ -4274,7 +4309,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>174</v>
       </c>
@@ -4297,7 +4332,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>176</v>
       </c>
@@ -4320,7 +4355,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>177</v>
       </c>
@@ -4343,7 +4378,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>180</v>
       </c>
@@ -4366,7 +4401,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>181</v>
       </c>
@@ -4389,7 +4424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>184</v>
       </c>
@@ -4412,7 +4447,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>186</v>
       </c>
@@ -4435,7 +4470,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>188</v>
       </c>
@@ -4458,7 +4493,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>189</v>
       </c>
@@ -4484,7 +4519,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>193</v>
       </c>
@@ -4510,7 +4545,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>194</v>
       </c>
@@ -4536,7 +4571,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>198</v>
       </c>
@@ -4562,7 +4597,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -4588,7 +4623,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>204</v>
       </c>
@@ -4614,7 +4649,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>207</v>
       </c>
@@ -4637,7 +4672,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>209</v>
       </c>
@@ -4660,7 +4695,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>211</v>
       </c>
@@ -4695,7 +4730,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>216</v>
       </c>
@@ -4730,7 +4765,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>219</v>
       </c>
@@ -4765,7 +4800,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>222</v>
       </c>
@@ -4800,7 +4835,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>60</v>
       </c>
@@ -4835,7 +4870,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -4870,7 +4905,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>62</v>
       </c>
@@ -4905,7 +4940,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -4940,7 +4975,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>234</v>
       </c>
@@ -4975,7 +5010,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>238</v>
       </c>
@@ -5010,7 +5045,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>241</v>
       </c>
@@ -5048,7 +5083,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -5080,7 +5115,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>247</v>
       </c>
@@ -5118,7 +5153,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>63</v>
       </c>
@@ -5153,7 +5188,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>251</v>
       </c>
@@ -5176,7 +5211,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>254</v>
       </c>
@@ -5199,7 +5234,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>255</v>
       </c>
@@ -5222,7 +5257,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>256</v>
       </c>
@@ -5245,7 +5280,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>259</v>
       </c>
@@ -5268,7 +5303,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>260</v>
       </c>
@@ -5291,7 +5326,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>262</v>
       </c>
@@ -5314,7 +5349,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -5346,7 +5381,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>64</v>
       </c>
@@ -5381,7 +5416,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>65</v>
       </c>
@@ -5410,7 +5445,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>269</v>
       </c>
@@ -5433,7 +5468,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>272</v>
       </c>
@@ -5456,7 +5491,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>274</v>
       </c>
@@ -5476,7 +5511,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>275</v>
       </c>
@@ -5496,7 +5531,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>276</v>
       </c>
@@ -5516,7 +5551,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>277</v>
       </c>
@@ -5536,7 +5571,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -5571,7 +5606,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -5606,7 +5641,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>67</v>
       </c>
@@ -5641,7 +5676,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -5676,7 +5711,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>12</v>
       </c>
@@ -5711,7 +5746,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>288</v>
       </c>
@@ -5734,7 +5769,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>68</v>
       </c>
@@ -5769,7 +5804,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>292</v>
       </c>
@@ -5795,7 +5830,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>295</v>
       </c>
@@ -5821,7 +5856,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>296</v>
       </c>
@@ -5844,7 +5879,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>298</v>
       </c>
@@ -5867,7 +5902,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -5896,7 +5931,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>69</v>
       </c>
@@ -5925,7 +5960,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>15</v>
       </c>
@@ -5960,7 +5995,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -5998,7 +6033,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>19</v>
       </c>
@@ -6033,7 +6068,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>20</v>
       </c>
@@ -6071,7 +6106,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -6103,7 +6138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>318</v>
       </c>
@@ -6129,7 +6164,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>23</v>
       </c>
@@ -6167,7 +6202,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>25</v>
       </c>
@@ -6202,7 +6237,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>70</v>
       </c>
@@ -6237,7 +6272,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>26</v>
       </c>
@@ -6269,7 +6304,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>28</v>
       </c>
@@ -6301,7 +6336,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -6333,7 +6368,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>71</v>
       </c>
@@ -6365,7 +6400,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>30</v>
       </c>
@@ -6397,7 +6432,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>341</v>
       </c>
@@ -6417,7 +6452,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>343</v>
       </c>
@@ -6437,7 +6472,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>344</v>
       </c>
@@ -6460,7 +6495,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>347</v>
       </c>
@@ -6483,7 +6518,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>31</v>
       </c>
@@ -6524,7 +6559,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>353</v>
       </c>
@@ -6553,7 +6588,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>358</v>
       </c>
@@ -6582,7 +6617,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -6605,7 +6640,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>362</v>
       </c>
@@ -6628,7 +6663,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>365</v>
       </c>
@@ -6651,7 +6686,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>366</v>
       </c>
@@ -6671,7 +6706,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>368</v>
       </c>
@@ -6697,7 +6732,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>372</v>
       </c>
@@ -6723,7 +6758,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>373</v>
       </c>
@@ -6752,7 +6787,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>35</v>
       </c>
@@ -6772,7 +6807,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -6807,7 +6842,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>380</v>
       </c>
@@ -6839,7 +6874,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>39</v>
       </c>
@@ -6867,29 +6902,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4A8A969-62BA-4715-B5A6-5ED2352DD30F}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>59</v>
       </c>
